--- a/dados/excel/municipio_percentis.xlsx
+++ b/dados/excel/municipio_percentis.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -882,28 +882,28 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>13829</v>
+        <v>14368</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>8491.74</v>
+        <v>8441.040000000001</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1118.4</v>
+        <v>1864</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>3858.38</v>
+        <v>3725.13</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>6343.41</v>
+        <v>6152.56</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>12110.74</v>
+        <v>11946.88</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>17031.62</v>
+        <v>16885.4</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>34294.54</v>
+        <v>34388.92</v>
       </c>
     </row>
   </sheetData>
